--- a/artfynd/A 21738-2026 artfynd.xlsx
+++ b/artfynd/A 21738-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>54795281</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -730,10 +725,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>657263.4944610785</v>
+        <v>657263</v>
       </c>
       <c r="R2" t="n">
-        <v>6640830.022580335</v>
+        <v>6640830</v>
       </c>
       <c r="S2" t="n">
         <v>16</v>
